--- a/nriss-patch-1/ig/CodeSystem-MinimalRuim.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-MinimalRuim.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T13:31:48+00:00</t>
+    <t>2026-03-30T13:39:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/CodeSystem-MinimalRuim.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-MinimalRuim.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T13:39:05+00:00</t>
+    <t>2026-03-30T13:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
